--- a/output/pdf_financials_xlsx/GQC.xlsx
+++ b/output/pdf_financials_xlsx/GQC.xlsx
@@ -1320,31 +1320,31 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.976255</v>
+        <v>-0.976255</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.086369</v>
+        <v>-2.086369</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.535759</v>
+        <v>-3.535759</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.0069</v>
+        <v>-8.0069</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>7.034553</v>
+        <v>-7.034553</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.945916</v>
+        <v>-4.945916</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>8.898611000000001</v>
+        <v>-8.898611000000001</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>10.444972</v>
+        <v>-10.444972</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-6.151652</v>
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.976255</v>
+        <v>-0.976255</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.086369</v>
+        <v>-2.086369</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.535759</v>
+        <v>-3.535759</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.0069</v>
+        <v>-8.0069</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7.034553</v>
+        <v>-7.034553</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.945916</v>
+        <v>-4.945916</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.898611000000001</v>
+        <v>-8.898611000000001</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.444972</v>
+        <v>-10.444972</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-6.151652</v>
@@ -1818,31 +1818,31 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.976255</v>
+        <v>-0.976255</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.086369</v>
+        <v>-2.086369</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.535759</v>
+        <v>-3.535759</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.0069</v>
+        <v>-8.0069</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7.034553</v>
+        <v>-7.034553</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.945916</v>
+        <v>-4.945916</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>8.898611000000001</v>
+        <v>-8.898611000000001</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>10.444972</v>
+        <v>-10.444972</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-6.151652</v>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>48.81275</v>
+        <v>-48.81275</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2148,31 +2148,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.976255</v>
+        <v>-0.976255</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.086369</v>
+        <v>-2.086369</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.535759</v>
+        <v>-3.535759</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8.0069</v>
+        <v>-8.0069</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.034553</v>
+        <v>-7.034553</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.945916</v>
+        <v>-4.945916</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8.898611000000001</v>
+        <v>-8.898611000000001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.444972</v>
+        <v>-10.444972</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-6.151652</v>
@@ -2274,31 +2274,31 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.976255</v>
+        <v>-0.976255</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.102486</v>
+        <v>-2.070252</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.599588</v>
+        <v>-3.47193</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.266555</v>
+        <v>-6.171719</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.127674000000001</v>
+        <v>-7.886126</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.148788</v>
+        <v>-6.920318</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.012232</v>
+        <v>-4.8796</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.949277</v>
+        <v>-8.847944999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.487686</v>
+        <v>-10.402258</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-6.108694</v>
@@ -2430,31 +2430,31 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -6185,25 +6185,25 @@
         <v>7.526539</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.09812700000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.557439</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.557439</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.7593569999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.901527</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.6181759999999999</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -6226,7 +6226,7 @@
         <v>19.035824</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>18.686264</v>
+        <v>22.787858</v>
       </c>
     </row>
     <row r="93">
@@ -6557,7 +6557,7 @@
         <v>-3.535759</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-8.0069</v>
@@ -10168,7 +10168,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -13054,7 +13058,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -18099,7 +18107,11 @@
           <t>Warrants reserve (note 10(c)) 98,127</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -50252,16 +50264,16 @@
         </is>
       </c>
       <c r="L420" s="5" t="n">
-        <v>4.945916</v>
+        <v>-4.945916</v>
       </c>
       <c r="M420" s="5" t="n">
-        <v>8.898611000000001</v>
+        <v>-8.898611000000001</v>
       </c>
       <c r="N420" s="5" t="n">
-        <v>10.444972</v>
+        <v>-10.444972</v>
       </c>
       <c r="O420" s="5" t="n">
-        <v>6.151652</v>
+        <v>-6.151652</v>
       </c>
       <c r="P420" t="inlineStr">
         <is>
@@ -50450,16 +50462,16 @@
         </is>
       </c>
       <c r="L422" s="5" t="n">
-        <v>4.942916</v>
+        <v>-4.942916</v>
       </c>
       <c r="M422" s="5" t="n">
-        <v>8.861110999999999</v>
+        <v>-8.861110999999999</v>
       </c>
       <c r="N422" s="5" t="n">
-        <v>10.480972</v>
+        <v>-10.480972</v>
       </c>
       <c r="O422" s="5" t="n">
-        <v>6.147152</v>
+        <v>-6.147152</v>
       </c>
       <c r="P422" t="inlineStr">
         <is>
@@ -52164,10 +52176,10 @@
         </is>
       </c>
       <c r="M439" s="5" t="n">
-        <v>8.898611000000001</v>
+        <v>-8.898611000000001</v>
       </c>
       <c r="N439" s="5" t="n">
-        <v>10.444972</v>
+        <v>-10.444972</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
@@ -53724,10 +53736,10 @@
         </is>
       </c>
       <c r="K455" s="5" t="n">
-        <v>7.034553</v>
+        <v>-7.034553</v>
       </c>
       <c r="L455" s="5" t="n">
-        <v>4.945916</v>
+        <v>-4.945916</v>
       </c>
       <c r="M455" t="inlineStr">
         <is>
@@ -54027,10 +54039,10 @@
         </is>
       </c>
       <c r="K458" s="5" t="n">
-        <v>7.186066</v>
+        <v>-7.186066</v>
       </c>
       <c r="L458" s="5" t="n">
-        <v>4.942916</v>
+        <v>-4.942916</v>
       </c>
       <c r="M458" t="inlineStr">
         <is>
@@ -54416,10 +54428,10 @@
         </is>
       </c>
       <c r="J462" s="5" t="n">
-        <v>8.0069</v>
+        <v>-8.0069</v>
       </c>
       <c r="K462" s="5" t="n">
-        <v>7.034553</v>
+        <v>-7.034553</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -54618,10 +54630,10 @@
         </is>
       </c>
       <c r="J464" s="5" t="n">
-        <v>7.855387</v>
+        <v>-7.855387</v>
       </c>
       <c r="K464" s="5" t="n">
-        <v>7.186066</v>
+        <v>-7.186066</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -55710,10 +55722,10 @@
         </is>
       </c>
       <c r="I475" s="5" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="J475" s="5" t="n">
-        <v>8.0069</v>
+        <v>-8.0069</v>
       </c>
       <c r="K475" t="inlineStr">
         <is>
@@ -55914,10 +55926,10 @@
         </is>
       </c>
       <c r="I477" s="5" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="J477" s="5" t="n">
-        <v>7.855387</v>
+        <v>-7.855387</v>
       </c>
       <c r="K477" t="inlineStr">
         <is>
@@ -57201,13 +57213,13 @@
         </is>
       </c>
       <c r="G490" s="5" t="n">
-        <v>2.086369</v>
+        <v>-2.086369</v>
       </c>
       <c r="H490" s="5" t="n">
-        <v>3.535759</v>
+        <v>-3.535759</v>
       </c>
       <c r="I490" s="5" t="n">
-        <v>6.219137</v>
+        <v>-6.219137</v>
       </c>
       <c r="J490" t="inlineStr">
         <is>
@@ -59794,10 +59806,10 @@
         </is>
       </c>
       <c r="F516" s="5" t="n">
-        <v>0.976255</v>
+        <v>-0.976255</v>
       </c>
       <c r="G516" s="5" t="n">
-        <v>0.974483</v>
+        <v>-0.974483</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GQC.xlsx
+++ b/output/pdf_financials_xlsx/GQC.xlsx
@@ -949,28 +949,28 @@
         <v>0.809366</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.017492</v>
+        <v>1.737141</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>3.191358</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.020894</v>
+        <v>6.922657</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.07913100000000001</v>
+        <v>8.097405999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.137785</v>
+        <v>6.26075</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.116396</v>
+        <v>4.884506</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.177071</v>
+        <v>8.936538000000001</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.24581</v>
+        <v>10.639329</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>5.162192</v>
@@ -1011,28 +1011,28 @@
         <v>-0.809366</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.017492</v>
+        <v>-1.737141</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-3.191358</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.020894</v>
+        <v>-6.922657</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.07913100000000001</v>
+        <v>-8.097405999999999</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.137785</v>
+        <v>-6.26075</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.116396</v>
+        <v>-4.884506</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.177071</v>
+        <v>-8.936538000000001</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.24581</v>
+        <v>-10.639329</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-5.162192</v>
@@ -1072,49 +1072,49 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010201</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006221</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012985</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035165</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09110600000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.059517</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014346</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037927</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.194357</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.257539</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.268557</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.053678</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.202882</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.452245</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.389635</v>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2148,46 +2148,46 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.976255</v>
+        <v>-0.966054</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.086369</v>
+        <v>-2.080148</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.535759</v>
+        <v>-3.522774</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.219137</v>
+        <v>-6.183972</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-8.0069</v>
+        <v>-7.915794</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-7.034553</v>
+        <v>-6.975036</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.945916</v>
+        <v>-4.93157</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-8.898611000000001</v>
+        <v>-8.860683999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-10.444972</v>
+        <v>-10.250615</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.151652</v>
+        <v>-6.409191</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.954295</v>
+        <v>-2.222852</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.395521</v>
+        <v>-2.449199</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.709298</v>
+        <v>-2.91218</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.583344</v>
+        <v>-3.035589</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2274,46 +2274,46 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.976255</v>
+        <v>-0.966054</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.070252</v>
+        <v>-2.064031</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.47193</v>
+        <v>-3.458945</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.171719</v>
+        <v>-6.136554</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-7.886126</v>
+        <v>-7.79502</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.920318</v>
+        <v>-6.860801</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.8796</v>
+        <v>-4.865254</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-8.847944999999999</v>
+        <v>-8.810017999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-10.402258</v>
+        <v>-10.207901</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.108694</v>
+        <v>-6.366233</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.911857</v>
+        <v>-2.180414</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.363922</v>
+        <v>-2.4176</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.685033</v>
+        <v>-2.887915</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.558477</v>
+        <v>-3.010722</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -8059,10 +8059,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.006601</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008486</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -8119,10 +8119,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.006601</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008486</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -36268,7 +36268,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -44388,7 +44392,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -49940,7 +49944,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -50029,7 +50033,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -51926,7 +51930,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -52029,7 +52033,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -55298,7 +55302,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -58389,7 +58393,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
